--- a/Sheets/Run-1a_MomBinnedBzResults.xlsx
+++ b/Sheets/Run-1a_MomBinnedBzResults.xlsx
@@ -8,19 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/samuelgrant/Documents/gm2/EDM/Sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B0625C0-9CF3-1B4D-B09E-9FB98EB96A29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{4DC24AD7-F336-0045-BDFF-59B8FEFA243F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11620" yWindow="1500" windowWidth="16800" windowHeight="15940"/>
+    <workbookView xWindow="360" yWindow="1220" windowWidth="16800" windowHeight="15940"/>
   </bookViews>
   <sheets>
     <sheet name="Run-1a_BzResults" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
   <si>
     <t xml:space="preserve"> delta_prime</t>
   </si>
@@ -47,6 +58,12 @@
   </si>
   <si>
     <t>S12S18</t>
+  </si>
+  <si>
+    <t>err d_Bz [mrad</t>
+  </si>
+  <si>
+    <t>combined error</t>
   </si>
 </sst>
 </file>
@@ -887,92 +904,155 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="13.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1">
+        <v>7.7696500000000002E-2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B3">
+      <c r="B4">
         <v>-4.4155399999999997E-2</v>
       </c>
-      <c r="C3">
+      <c r="C4">
         <v>0.107613</v>
       </c>
-      <c r="D3">
+      <c r="D4">
+        <f>SQRT($B$1^2+C4^2)</f>
+        <v>0.13273019204856898</v>
+      </c>
+      <c r="E4">
         <v>-44.1554</v>
       </c>
-      <c r="E3">
+      <c r="F4">
         <v>107.613</v>
       </c>
+      <c r="G4">
+        <f>B4*1000</f>
+        <v>-44.1554</v>
+      </c>
+      <c r="H4">
+        <f>C4*1000</f>
+        <v>107.613</v>
+      </c>
+      <c r="I4">
+        <f>D4*1000</f>
+        <v>132.73019204856897</v>
+      </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B4">
+      <c r="B5">
         <v>4.5900299999999998E-2</v>
       </c>
-      <c r="C4">
+      <c r="C5">
         <v>0.112274</v>
       </c>
-      <c r="D4">
+      <c r="D5">
+        <f t="shared" ref="D5:D6" si="0">SQRT($B$1^2+C5^2)</f>
+        <v>0.13653643172519925</v>
+      </c>
+      <c r="E5">
         <v>45.900300000000001</v>
       </c>
-      <c r="E4">
+      <c r="F5">
         <v>112.274</v>
       </c>
+      <c r="G5">
+        <f t="shared" ref="G5:G6" si="1">B5*1000</f>
+        <v>45.900300000000001</v>
+      </c>
+      <c r="H5">
+        <f t="shared" ref="H5:H6" si="2">C5*1000</f>
+        <v>112.274</v>
+      </c>
+      <c r="I5">
+        <f t="shared" ref="I5:I6" si="3">D5*1000</f>
+        <v>136.53643172519924</v>
+      </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <v>-1.60505E-3</v>
       </c>
-      <c r="C5">
+      <c r="C6">
         <v>7.7696500000000002E-2</v>
       </c>
-      <c r="D5">
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>0.10987944404892118</v>
+      </c>
+      <c r="E6">
         <v>-1.6050500000000001</v>
       </c>
-      <c r="E5">
+      <c r="F6">
         <v>77.6965</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="1"/>
+        <v>-1.6050500000000001</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="2"/>
+        <v>77.6965</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="3"/>
+        <v>109.87944404892117</v>
       </c>
     </row>
   </sheetData>
